--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_talk.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_talk.xlsx
@@ -102,11 +102,11 @@
       <rPr>
         <sz val="10"/>
         <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">~</t>
+        <rFont val="游ゴシック"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">～</t>
     </r>
   </si>
   <si>
@@ -1244,29 +1244,10 @@
     <t xml:space="preserve">pervert4</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">뭐 이런 변태가 다 있담.
+    <t xml:space="preserve">뭐 이런 변태가 다 있담.
 이런이런.
-흐</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">ー음…?
+흐ー음…?
 그래, 나한테?</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">pervert3</t>
@@ -2250,9 +2231,9 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="128"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2264,9 +2245,9 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
-      <charset val="129"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2336,7 +2317,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -4014,7 +3995,6 @@
       <c r="B40" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="C40" s="5"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>

--- a/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_talk.xlsx
+++ b/DIFF_PREVIOUS/Mod_Korean/Lang/KR/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$135</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$136</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="303">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -85,32 +85,22 @@
     <t xml:space="preserve">hope</t>
   </si>
   <si>
+    <t xml:space="preserve">ahoy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">아호이!
+출항!
+승선하라!
+가자!</t>
+  </si>
+  <si>
     <t xml:space="preserve">fusion</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">삐갸앗!
+    <t xml:space="preserve">삐갸앗!
 삐갸아아앗!
-삐갸아아</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <rFont val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">ー아아!
+삐갸아아ー아아!
 삐…</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">play_baby</t>
@@ -2339,7 +2329,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -2363,13 +2353,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="游ゴシック"/>
-      <family val="2"/>
       <charset val="129"/>
     </font>
     <font>
@@ -2450,7 +2433,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2458,7 +2441,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2506,9 +2489,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>409680</xdr:colOff>
+      <xdr:colOff>2374200</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>123480</xdr:rowOff>
+      <xdr:rowOff>122400</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2518,7 +2501,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50979960" cy="123480"/>
+          <a:ext cx="50978880" cy="122400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2551,9 +2534,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>514800</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>61920</xdr:rowOff>
+      <xdr:colOff>513720</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>60840</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -2563,7 +2546,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="57472920" cy="46313280"/>
+          <a:ext cx="55506600" cy="46861560"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
@@ -2698,11 +2681,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CM136"/>
+  <dimension ref="A1:CM137"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="67.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="39.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="36.48"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="47.19"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="61.1"/>
@@ -2911,7 +2894,7 @@
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -2947,7 +2930,7 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2983,11 +2966,11 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="U7" s="3"/>
@@ -3019,11 +3002,11 @@
       <c r="AU7" s="3"/>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>29</v>
       </c>
       <c r="U8" s="3"/>
@@ -3055,7 +3038,7 @@
       <c r="AU8" s="3"/>
       <c r="AV8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
@@ -3091,11 +3074,11 @@
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="4" t="s">
         <v>33</v>
       </c>
       <c r="U10" s="3"/>
@@ -3167,7 +3150,7 @@
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="1" t="s">
         <v>37</v>
       </c>
       <c r="U12" s="3"/>
@@ -3199,11 +3182,11 @@
       <c r="AU12" s="3"/>
       <c r="AV12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>39</v>
       </c>
       <c r="U13" s="3"/>
@@ -3235,7 +3218,7 @@
       <c r="AU13" s="3"/>
       <c r="AV13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
@@ -3271,34 +3254,43 @@
       <c r="AU14" s="3"/>
       <c r="AV14" s="3"/>
     </row>
-    <row r="15" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="AW15" s="1"/>
-    </row>
-    <row r="16" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U15" s="3"/>
+      <c r="V15" s="3"/>
+      <c r="W15" s="3"/>
+      <c r="X15" s="3"/>
+      <c r="Y15" s="3"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
+      <c r="AB15" s="3"/>
+      <c r="AC15" s="3"/>
+      <c r="AD15" s="3"/>
+      <c r="AE15" s="3"/>
+      <c r="AF15" s="3"/>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3"/>
+      <c r="AJ15" s="3"/>
+      <c r="AK15" s="3"/>
+      <c r="AL15" s="3"/>
+      <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+      <c r="AO15" s="3"/>
+      <c r="AP15" s="3"/>
+      <c r="AQ15" s="3"/>
+      <c r="AR15" s="3"/>
+      <c r="AS15" s="3"/>
+      <c r="AT15" s="3"/>
+      <c r="AU15" s="3"/>
+      <c r="AV15" s="3"/>
+    </row>
+    <row r="16" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
@@ -3352,7 +3344,7 @@
       <c r="T17" s="1"/>
       <c r="AW17" s="1"/>
     </row>
-    <row r="18" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -3379,7 +3371,7 @@
       <c r="T18" s="1"/>
       <c r="AW18" s="1"/>
     </row>
-    <row r="19" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -3406,7 +3398,7 @@
       <c r="T19" s="1"/>
       <c r="AW19" s="1"/>
     </row>
-    <row r="20" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
@@ -3433,50 +3425,40 @@
       <c r="T20" s="1"/>
       <c r="AW20" s="1"/>
     </row>
-    <row r="21" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-      <c r="AA21" s="3"/>
-      <c r="AB21" s="3"/>
-      <c r="AC21" s="3"/>
-      <c r="AD21" s="3"/>
-      <c r="AE21" s="3"/>
-      <c r="AF21" s="3"/>
-      <c r="AG21" s="3"/>
-      <c r="AH21" s="3"/>
-      <c r="AI21" s="3"/>
-      <c r="AJ21" s="3"/>
-      <c r="AK21" s="3"/>
-      <c r="AL21" s="3"/>
-      <c r="AM21" s="3"/>
-      <c r="AN21" s="3"/>
-      <c r="AO21" s="3"/>
-      <c r="AP21" s="3"/>
-      <c r="AQ21" s="3"/>
-      <c r="AR21" s="3"/>
-      <c r="AS21" s="3"/>
-      <c r="AT21" s="3"/>
-      <c r="AU21" s="3"/>
-      <c r="AV21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="AW21" s="1"/>
+    </row>
+    <row r="22" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="4"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -3506,8 +3488,8 @@
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B23" s="4" t="s">
@@ -3543,7 +3525,7 @@
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="4" t="s">
         <v>60</v>
       </c>
@@ -3580,7 +3562,7 @@
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="4" t="s">
         <v>62</v>
       </c>
@@ -3618,7 +3600,7 @@
       <c r="AV25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -3654,13 +3636,14 @@
       <c r="AU26" s="3"/>
       <c r="AV26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>67</v>
       </c>
+      <c r="C27" s="4"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -3690,11 +3673,11 @@
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="4" t="s">
         <v>69</v>
       </c>
       <c r="U28" s="3"/>
@@ -3726,14 +3709,13 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="146.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>70</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C29" s="7"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3763,13 +3745,14 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="146.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="7" t="s">
         <v>73</v>
       </c>
+      <c r="C30" s="7"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3799,14 +3782,13 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>74</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C31" s="4"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3836,13 +3818,14 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>76</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>77</v>
       </c>
+      <c r="C32" s="4"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3872,7 +3855,7 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>78</v>
       </c>
@@ -3908,7 +3891,7 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
@@ -3944,7 +3927,7 @@
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
@@ -3980,14 +3963,13 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="4"/>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -4017,13 +3999,14 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="1" t="s">
         <v>87</v>
       </c>
+      <c r="C37" s="4"/>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -4053,7 +4036,7 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>88</v>
       </c>
@@ -4089,7 +4072,7 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>90</v>
       </c>
@@ -4125,7 +4108,7 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>92</v>
       </c>
@@ -4161,7 +4144,7 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>94</v>
       </c>
@@ -4197,11 +4180,11 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="4" t="s">
         <v>97</v>
       </c>
       <c r="U42" s="3"/>
@@ -4233,11 +4216,11 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="1" t="s">
         <v>99</v>
       </c>
       <c r="U43" s="3"/>
@@ -4269,7 +4252,7 @@
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>100</v>
       </c>
@@ -4305,7 +4288,7 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>102</v>
       </c>
@@ -4341,7 +4324,7 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>104</v>
       </c>
@@ -4377,7 +4360,7 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>106</v>
       </c>
@@ -4413,7 +4396,7 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>108</v>
       </c>
@@ -4449,15 +4432,12 @@
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>111</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>112</v>
       </c>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
@@ -4488,11 +4468,14 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="C50" s="4" t="s">
         <v>114</v>
       </c>
       <c r="U50" s="3"/>
@@ -4524,11 +4507,11 @@
       <c r="AU50" s="3"/>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="1" t="s">
         <v>116</v>
       </c>
       <c r="U51" s="3"/>
@@ -4596,31 +4579,13 @@
       <c r="AU52" s="3"/>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+    <row r="53" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-      <c r="O53" s="6"/>
-      <c r="P53" s="6"/>
-      <c r="Q53" s="6"/>
-      <c r="R53" s="6"/>
-      <c r="S53" s="6"/>
-      <c r="T53" s="6"/>
       <c r="U53" s="3"/>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4650,11 +4615,11 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="6" t="s">
         <v>122</v>
       </c>
       <c r="C54" s="6"/>
@@ -4704,7 +4669,7 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="s">
         <v>123</v>
       </c>
@@ -4758,7 +4723,7 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="s">
         <v>125</v>
       </c>
@@ -4812,7 +4777,7 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="s">
         <v>127</v>
       </c>
@@ -4920,11 +4885,11 @@
       <c r="AU58" s="3"/>
       <c r="AV58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C59" s="6"/>
@@ -4974,14 +4939,14 @@
       <c r="AU59" s="3"/>
       <c r="AV59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="C60" s="4"/>
+      <c r="C60" s="6"/>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
       <c r="F60" s="6"/>
@@ -5028,13 +4993,31 @@
       <c r="AU60" s="3"/>
       <c r="AV60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+    <row r="61" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="4" t="s">
         <v>136</v>
       </c>
+      <c r="C61" s="4"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="6"/>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6"/>
+      <c r="H61" s="6"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="6"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="6"/>
+      <c r="T61" s="6"/>
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
@@ -5208,11 +5191,11 @@
       <c r="AU65" s="3"/>
       <c r="AV65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="1" t="s">
         <v>146</v>
       </c>
       <c r="U66" s="3"/>
@@ -5244,11 +5227,11 @@
       <c r="AU66" s="3"/>
       <c r="AV66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="4" t="s">
         <v>148</v>
       </c>
       <c r="U67" s="3"/>
@@ -5280,11 +5263,11 @@
       <c r="AU67" s="3"/>
       <c r="AV67" s="3"/>
     </row>
-    <row r="68" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="1" t="s">
         <v>150</v>
       </c>
       <c r="U68" s="3"/>
@@ -5316,11 +5299,11 @@
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="4" t="s">
         <v>152</v>
       </c>
       <c r="U69" s="3"/>
@@ -5424,11 +5407,11 @@
       <c r="AU71" s="3"/>
       <c r="AV71" s="3"/>
     </row>
-    <row r="72" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="1" t="s">
         <v>158</v>
       </c>
       <c r="U72" s="3"/>
@@ -5460,9 +5443,12 @@
       <c r="AU72" s="3"/>
       <c r="AV72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>159</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>160</v>
       </c>
       <c r="U73" s="3"/>
       <c r="V73" s="3"/>
@@ -5493,11 +5479,8 @@
       <c r="AU73" s="3"/>
       <c r="AV73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B74" s="4" t="s">
         <v>161</v>
       </c>
       <c r="U74" s="3"/>
@@ -5529,11 +5512,11 @@
       <c r="AU74" s="3"/>
       <c r="AV74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="4" t="s">
         <v>163</v>
       </c>
       <c r="U75" s="3"/>
@@ -5564,54 +5547,13 @@
       <c r="AT75" s="3"/>
       <c r="AU75" s="3"/>
       <c r="AV75" s="3"/>
-      <c r="AY75" s="3"/>
-      <c r="AZ75" s="3"/>
-      <c r="BA75" s="3"/>
-      <c r="BB75" s="3"/>
-      <c r="BC75" s="3"/>
-      <c r="BD75" s="3"/>
-      <c r="BE75" s="3"/>
-      <c r="BF75" s="3"/>
-      <c r="BG75" s="3"/>
-      <c r="BH75" s="3"/>
-      <c r="BI75" s="3"/>
-      <c r="BJ75" s="3"/>
-      <c r="BK75" s="3"/>
-      <c r="BL75" s="3"/>
-      <c r="BM75" s="3"/>
-      <c r="BN75" s="3"/>
-      <c r="BO75" s="3"/>
-      <c r="BP75" s="3"/>
-      <c r="BQ75" s="3"/>
-      <c r="BR75" s="3"/>
-      <c r="BS75" s="3"/>
-      <c r="BT75" s="3"/>
-      <c r="BU75" s="3"/>
-      <c r="BV75" s="3"/>
-      <c r="BW75" s="3"/>
-      <c r="BX75" s="3"/>
-      <c r="BY75" s="3"/>
-      <c r="BZ75" s="3"/>
-      <c r="CA75" s="3"/>
-      <c r="CB75" s="3"/>
-      <c r="CC75" s="3"/>
-      <c r="CD75" s="3"/>
-      <c r="CE75" s="3"/>
-      <c r="CF75" s="3"/>
-      <c r="CG75" s="3"/>
-      <c r="CH75" s="3"/>
-      <c r="CI75" s="3"/>
-      <c r="CJ75" s="3"/>
-      <c r="CK75" s="3"/>
-      <c r="CL75" s="3"/>
-      <c r="CM75" s="3"/>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>164</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="U76" s="3"/>
       <c r="V76" s="3"/>
@@ -5685,10 +5627,10 @@
     </row>
     <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="U77" s="3"/>
       <c r="V77" s="3"/>
@@ -5760,11 +5702,11 @@
       <c r="CL77" s="3"/>
       <c r="CM77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="1" t="s">
         <v>168</v>
       </c>
       <c r="U78" s="3"/>
@@ -5837,7 +5779,7 @@
       <c r="CL78" s="3"/>
       <c r="CM78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>169</v>
       </c>
@@ -5914,7 +5856,7 @@
       <c r="CL79" s="3"/>
       <c r="CM79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>171</v>
       </c>
@@ -5991,7 +5933,7 @@
       <c r="CL80" s="3"/>
       <c r="CM80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>173</v>
       </c>
@@ -6068,7 +6010,7 @@
       <c r="CL81" s="3"/>
       <c r="CM81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
         <v>175</v>
       </c>
@@ -6145,11 +6087,11 @@
       <c r="CL82" s="3"/>
       <c r="CM82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="4" t="s">
         <v>178</v>
       </c>
       <c r="U83" s="3"/>
@@ -6222,11 +6164,11 @@
       <c r="CL83" s="3"/>
       <c r="CM83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="1" t="s">
         <v>180</v>
       </c>
       <c r="U84" s="3"/>
@@ -6299,11 +6241,11 @@
       <c r="CL84" s="3"/>
       <c r="CM84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="4" t="s">
         <v>182</v>
       </c>
       <c r="U85" s="3"/>
@@ -6761,11 +6703,11 @@
       <c r="CL90" s="3"/>
       <c r="CM90" s="3"/>
     </row>
-    <row r="91" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="1" t="s">
         <v>194</v>
       </c>
       <c r="U91" s="3"/>
@@ -6838,11 +6780,11 @@
       <c r="CL91" s="3"/>
       <c r="CM91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="4" t="s">
         <v>196</v>
       </c>
       <c r="U92" s="3"/>
@@ -6915,11 +6857,11 @@
       <c r="CL92" s="3"/>
       <c r="CM92" s="3"/>
     </row>
-    <row r="93" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="1" t="s">
         <v>198</v>
       </c>
       <c r="U93" s="3"/>
@@ -6992,13 +6934,41 @@
       <c r="CL93" s="3"/>
       <c r="CM93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="4" t="s">
         <v>200</v>
       </c>
+      <c r="U94" s="3"/>
+      <c r="V94" s="3"/>
+      <c r="W94" s="3"/>
+      <c r="X94" s="3"/>
+      <c r="Y94" s="3"/>
+      <c r="Z94" s="3"/>
+      <c r="AA94" s="3"/>
+      <c r="AB94" s="3"/>
+      <c r="AC94" s="3"/>
+      <c r="AD94" s="3"/>
+      <c r="AE94" s="3"/>
+      <c r="AF94" s="3"/>
+      <c r="AG94" s="3"/>
+      <c r="AH94" s="3"/>
+      <c r="AI94" s="3"/>
+      <c r="AJ94" s="3"/>
+      <c r="AK94" s="3"/>
+      <c r="AL94" s="3"/>
+      <c r="AM94" s="3"/>
+      <c r="AN94" s="3"/>
+      <c r="AO94" s="3"/>
+      <c r="AP94" s="3"/>
+      <c r="AQ94" s="3"/>
+      <c r="AR94" s="3"/>
+      <c r="AS94" s="3"/>
+      <c r="AT94" s="3"/>
+      <c r="AU94" s="3"/>
+      <c r="AV94" s="3"/>
       <c r="AY94" s="3"/>
       <c r="AZ94" s="3"/>
       <c r="BA94" s="3"/>
@@ -7091,8 +7061,11 @@
       <c r="CM95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="4" t="s">
+      <c r="A96" s="1" t="s">
         <v>203</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="AY96" s="3"/>
       <c r="AZ96" s="3"/>
@@ -7136,11 +7109,8 @@
       <c r="CL96" s="3"/>
       <c r="CM96" s="3"/>
     </row>
-    <row r="97" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="B97" s="4" t="s">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="4" t="s">
         <v>205</v>
       </c>
       <c r="AY97" s="3"/>
@@ -7185,11 +7155,11 @@
       <c r="CL97" s="3"/>
       <c r="CM97" s="3"/>
     </row>
-    <row r="98" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="335.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="4" t="s">
         <v>207</v>
       </c>
       <c r="AY98" s="3"/>
@@ -7234,11 +7204,11 @@
       <c r="CL98" s="3"/>
       <c r="CM98" s="3"/>
     </row>
-    <row r="99" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="1" t="s">
         <v>209</v>
       </c>
       <c r="AY99" s="3"/>
@@ -7283,31 +7253,13 @@
       <c r="CL99" s="3"/>
       <c r="CM99" s="3"/>
     </row>
-    <row r="100" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="6" t="s">
+    <row r="100" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
         <v>210</v>
       </c>
       <c r="B100" s="4" t="s">
         <v>211</v>
       </c>
-      <c r="C100" s="6"/>
-      <c r="D100" s="6"/>
-      <c r="E100" s="6"/>
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
-      <c r="M100" s="6"/>
-      <c r="N100" s="6"/>
-      <c r="O100" s="6"/>
-      <c r="P100" s="6"/>
-      <c r="Q100" s="6"/>
-      <c r="R100" s="6"/>
-      <c r="S100" s="6"/>
-      <c r="T100" s="6"/>
       <c r="AY100" s="3"/>
       <c r="AZ100" s="3"/>
       <c r="BA100" s="3"/>
@@ -7350,13 +7302,31 @@
       <c r="CL100" s="3"/>
       <c r="CM100" s="3"/>
     </row>
-    <row r="101" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+    <row r="101" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="6" t="s">
         <v>212</v>
       </c>
       <c r="B101" s="4" t="s">
         <v>213</v>
       </c>
+      <c r="C101" s="6"/>
+      <c r="D101" s="6"/>
+      <c r="E101" s="6"/>
+      <c r="F101" s="6"/>
+      <c r="G101" s="6"/>
+      <c r="H101" s="6"/>
+      <c r="I101" s="6"/>
+      <c r="J101" s="6"/>
+      <c r="K101" s="6"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="6"/>
+      <c r="N101" s="6"/>
+      <c r="O101" s="6"/>
+      <c r="P101" s="6"/>
+      <c r="Q101" s="6"/>
+      <c r="R101" s="6"/>
+      <c r="S101" s="6"/>
+      <c r="T101" s="6"/>
       <c r="AY101" s="3"/>
       <c r="AZ101" s="3"/>
       <c r="BA101" s="3"/>
@@ -7448,112 +7418,112 @@
       <c r="CL102" s="3"/>
       <c r="CM102" s="3"/>
     </row>
-    <row r="103" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>216</v>
       </c>
       <c r="B103" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1"/>
-      <c r="G103" s="1"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
-      <c r="J103" s="1"/>
-      <c r="K103" s="1"/>
-      <c r="L103" s="1"/>
-      <c r="M103" s="1"/>
-      <c r="N103" s="1"/>
-      <c r="O103" s="1"/>
-      <c r="P103" s="1"/>
-      <c r="Q103" s="1"/>
-      <c r="R103" s="1"/>
-      <c r="S103" s="1"/>
-      <c r="T103" s="1"/>
-      <c r="U103" s="1"/>
-      <c r="V103" s="1"/>
-      <c r="W103" s="1"/>
-      <c r="X103" s="1"/>
-      <c r="Y103" s="1"/>
-      <c r="Z103" s="1"/>
-      <c r="AA103" s="1"/>
-      <c r="AB103" s="1"/>
-      <c r="AC103" s="1"/>
-      <c r="AD103" s="1"/>
-      <c r="AE103" s="1"/>
-      <c r="AF103" s="1"/>
-      <c r="AG103" s="1"/>
-      <c r="AH103" s="1"/>
-      <c r="AI103" s="1"/>
-      <c r="AJ103" s="1"/>
-      <c r="AK103" s="1"/>
-      <c r="AL103" s="1"/>
-      <c r="AM103" s="1"/>
-      <c r="AN103" s="1"/>
-      <c r="AO103" s="1"/>
-      <c r="AP103" s="1"/>
-      <c r="AQ103" s="1"/>
-      <c r="AR103" s="1"/>
-      <c r="AS103" s="1"/>
-      <c r="AT103" s="1"/>
-      <c r="AU103" s="1"/>
-      <c r="AV103" s="1"/>
-      <c r="AW103" s="1"/>
-      <c r="AX103" s="1"/>
-    </row>
-    <row r="104" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY103" s="3"/>
+      <c r="AZ103" s="3"/>
+      <c r="BA103" s="3"/>
+      <c r="BB103" s="3"/>
+      <c r="BC103" s="3"/>
+      <c r="BD103" s="3"/>
+      <c r="BE103" s="3"/>
+      <c r="BF103" s="3"/>
+      <c r="BG103" s="3"/>
+      <c r="BH103" s="3"/>
+      <c r="BI103" s="3"/>
+      <c r="BJ103" s="3"/>
+      <c r="BK103" s="3"/>
+      <c r="BL103" s="3"/>
+      <c r="BM103" s="3"/>
+      <c r="BN103" s="3"/>
+      <c r="BO103" s="3"/>
+      <c r="BP103" s="3"/>
+      <c r="BQ103" s="3"/>
+      <c r="BR103" s="3"/>
+      <c r="BS103" s="3"/>
+      <c r="BT103" s="3"/>
+      <c r="BU103" s="3"/>
+      <c r="BV103" s="3"/>
+      <c r="BW103" s="3"/>
+      <c r="BX103" s="3"/>
+      <c r="BY103" s="3"/>
+      <c r="BZ103" s="3"/>
+      <c r="CA103" s="3"/>
+      <c r="CB103" s="3"/>
+      <c r="CC103" s="3"/>
+      <c r="CD103" s="3"/>
+      <c r="CE103" s="3"/>
+      <c r="CF103" s="3"/>
+      <c r="CG103" s="3"/>
+      <c r="CH103" s="3"/>
+      <c r="CI103" s="3"/>
+      <c r="CJ103" s="3"/>
+      <c r="CK103" s="3"/>
+      <c r="CL103" s="3"/>
+      <c r="CM103" s="3"/>
+    </row>
+    <row r="104" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>218</v>
       </c>
       <c r="B104" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="AY104" s="3"/>
-      <c r="AZ104" s="3"/>
-      <c r="BA104" s="3"/>
-      <c r="BB104" s="3"/>
-      <c r="BC104" s="3"/>
-      <c r="BD104" s="3"/>
-      <c r="BE104" s="3"/>
-      <c r="BF104" s="3"/>
-      <c r="BG104" s="3"/>
-      <c r="BH104" s="3"/>
-      <c r="BI104" s="3"/>
-      <c r="BJ104" s="3"/>
-      <c r="BK104" s="3"/>
-      <c r="BL104" s="3"/>
-      <c r="BM104" s="3"/>
-      <c r="BN104" s="3"/>
-      <c r="BO104" s="3"/>
-      <c r="BP104" s="3"/>
-      <c r="BQ104" s="3"/>
-      <c r="BR104" s="3"/>
-      <c r="BS104" s="3"/>
-      <c r="BT104" s="3"/>
-      <c r="BU104" s="3"/>
-      <c r="BV104" s="3"/>
-      <c r="BW104" s="3"/>
-      <c r="BX104" s="3"/>
-      <c r="BY104" s="3"/>
-      <c r="BZ104" s="3"/>
-      <c r="CA104" s="3"/>
-      <c r="CB104" s="3"/>
-      <c r="CC104" s="3"/>
-      <c r="CD104" s="3"/>
-      <c r="CE104" s="3"/>
-      <c r="CF104" s="3"/>
-      <c r="CG104" s="3"/>
-      <c r="CH104" s="3"/>
-      <c r="CI104" s="3"/>
-      <c r="CJ104" s="3"/>
-      <c r="CK104" s="3"/>
-      <c r="CL104" s="3"/>
-      <c r="CM104" s="3"/>
-    </row>
-    <row r="105" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C104" s="1"/>
+      <c r="D104" s="1"/>
+      <c r="E104" s="1"/>
+      <c r="F104" s="1"/>
+      <c r="G104" s="1"/>
+      <c r="H104" s="1"/>
+      <c r="I104" s="1"/>
+      <c r="J104" s="1"/>
+      <c r="K104" s="1"/>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="O104" s="1"/>
+      <c r="P104" s="1"/>
+      <c r="Q104" s="1"/>
+      <c r="R104" s="1"/>
+      <c r="S104" s="1"/>
+      <c r="T104" s="1"/>
+      <c r="U104" s="1"/>
+      <c r="V104" s="1"/>
+      <c r="W104" s="1"/>
+      <c r="X104" s="1"/>
+      <c r="Y104" s="1"/>
+      <c r="Z104" s="1"/>
+      <c r="AA104" s="1"/>
+      <c r="AB104" s="1"/>
+      <c r="AC104" s="1"/>
+      <c r="AD104" s="1"/>
+      <c r="AE104" s="1"/>
+      <c r="AF104" s="1"/>
+      <c r="AG104" s="1"/>
+      <c r="AH104" s="1"/>
+      <c r="AI104" s="1"/>
+      <c r="AJ104" s="1"/>
+      <c r="AK104" s="1"/>
+      <c r="AL104" s="1"/>
+      <c r="AM104" s="1"/>
+      <c r="AN104" s="1"/>
+      <c r="AO104" s="1"/>
+      <c r="AP104" s="1"/>
+      <c r="AQ104" s="1"/>
+      <c r="AR104" s="1"/>
+      <c r="AS104" s="1"/>
+      <c r="AT104" s="1"/>
+      <c r="AU104" s="1"/>
+      <c r="AV104" s="1"/>
+      <c r="AW104" s="1"/>
+      <c r="AX104" s="1"/>
+    </row>
+    <row r="105" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
         <v>220</v>
       </c>
@@ -7602,42 +7572,65 @@
       <c r="CL105" s="3"/>
       <c r="CM105" s="3"/>
     </row>
-    <row r="106" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>222</v>
       </c>
       <c r="B106" s="4" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="107" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY106" s="3"/>
+      <c r="AZ106" s="3"/>
+      <c r="BA106" s="3"/>
+      <c r="BB106" s="3"/>
+      <c r="BC106" s="3"/>
+      <c r="BD106" s="3"/>
+      <c r="BE106" s="3"/>
+      <c r="BF106" s="3"/>
+      <c r="BG106" s="3"/>
+      <c r="BH106" s="3"/>
+      <c r="BI106" s="3"/>
+      <c r="BJ106" s="3"/>
+      <c r="BK106" s="3"/>
+      <c r="BL106" s="3"/>
+      <c r="BM106" s="3"/>
+      <c r="BN106" s="3"/>
+      <c r="BO106" s="3"/>
+      <c r="BP106" s="3"/>
+      <c r="BQ106" s="3"/>
+      <c r="BR106" s="3"/>
+      <c r="BS106" s="3"/>
+      <c r="BT106" s="3"/>
+      <c r="BU106" s="3"/>
+      <c r="BV106" s="3"/>
+      <c r="BW106" s="3"/>
+      <c r="BX106" s="3"/>
+      <c r="BY106" s="3"/>
+      <c r="BZ106" s="3"/>
+      <c r="CA106" s="3"/>
+      <c r="CB106" s="3"/>
+      <c r="CC106" s="3"/>
+      <c r="CD106" s="3"/>
+      <c r="CE106" s="3"/>
+      <c r="CF106" s="3"/>
+      <c r="CG106" s="3"/>
+      <c r="CH106" s="3"/>
+      <c r="CI106" s="3"/>
+      <c r="CJ106" s="3"/>
+      <c r="CK106" s="3"/>
+      <c r="CL106" s="3"/>
+      <c r="CM106" s="3"/>
+    </row>
+    <row r="107" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
         <v>224</v>
       </c>
       <c r="B107" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="4"/>
-      <c r="L107" s="4"/>
-      <c r="M107" s="4"/>
-      <c r="N107" s="4"/>
-      <c r="O107" s="4"/>
-      <c r="P107" s="4"/>
-      <c r="Q107" s="4"/>
-      <c r="R107" s="4"/>
-      <c r="S107" s="4"/>
-      <c r="T107" s="4"/>
-    </row>
-    <row r="108" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="5" t="s">
+    </row>
+    <row r="108" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
         <v>226</v>
       </c>
       <c r="B108" s="4" t="s">
@@ -7662,8 +7655,8 @@
       <c r="S108" s="4"/>
       <c r="T108" s="4"/>
     </row>
-    <row r="109" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+    <row r="109" customFormat="false" ht="241.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="5" t="s">
         <v>228</v>
       </c>
       <c r="B109" s="4" t="s">
@@ -7688,23 +7681,41 @@
       <c r="S109" s="4"/>
       <c r="T109" s="4"/>
     </row>
-    <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B110" s="1" t="s">
+      <c r="B110" s="4" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="4"/>
+      <c r="D110" s="4"/>
+      <c r="E110" s="4"/>
+      <c r="F110" s="4"/>
+      <c r="G110" s="4"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
+      <c r="J110" s="4"/>
+      <c r="K110" s="4"/>
+      <c r="L110" s="4"/>
+      <c r="M110" s="4"/>
+      <c r="N110" s="4"/>
+      <c r="O110" s="4"/>
+      <c r="P110" s="4"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="4"/>
+      <c r="S110" s="4"/>
+      <c r="T110" s="4"/>
+    </row>
+    <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="1" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
         <v>234</v>
       </c>
@@ -7712,31 +7723,13 @@
         <v>235</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>236</v>
       </c>
       <c r="B113" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
-      <c r="K113" s="4"/>
-      <c r="L113" s="4"/>
-      <c r="M113" s="4"/>
-      <c r="N113" s="4"/>
-      <c r="O113" s="4"/>
-      <c r="P113" s="4"/>
-      <c r="Q113" s="4"/>
-      <c r="R113" s="4"/>
-      <c r="S113" s="4"/>
-      <c r="T113" s="4"/>
     </row>
     <row r="114" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
@@ -7764,77 +7757,95 @@
       <c r="S114" s="4"/>
       <c r="T114" s="4"/>
     </row>
-    <row r="115" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="s">
         <v>240</v>
       </c>
       <c r="B115" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C115" s="4" t="s">
+      <c r="C115" s="4"/>
+      <c r="D115" s="4"/>
+      <c r="E115" s="4"/>
+      <c r="F115" s="4"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="4"/>
+      <c r="I115" s="4"/>
+      <c r="J115" s="4"/>
+      <c r="K115" s="4"/>
+      <c r="L115" s="4"/>
+      <c r="M115" s="4"/>
+      <c r="N115" s="4"/>
+      <c r="O115" s="4"/>
+      <c r="P115" s="4"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="4"/>
+      <c r="S115" s="4"/>
+      <c r="T115" s="4"/>
+    </row>
+    <row r="116" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="D115" s="4" t="s">
+      <c r="B116" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="E115" s="4" t="s">
+      <c r="C116" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="F115" s="4" t="s">
+      <c r="D116" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="G115" s="4" t="s">
+      <c r="E116" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="H115" s="4" t="s">
+      <c r="F116" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="I115" s="4" t="s">
+      <c r="G116" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="J115" s="4" t="s">
+      <c r="H116" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="K115" s="4" t="s">
+      <c r="I116" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="L115" s="4" t="s">
+      <c r="J116" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="M115" s="4" t="s">
+      <c r="K116" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="N115" s="4" t="s">
+      <c r="L116" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="O115" s="4" t="s">
+      <c r="M116" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="P115" s="4" t="s">
+      <c r="N116" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="Q115" s="4" t="s">
+      <c r="O116" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="R115" s="4" t="s">
+      <c r="P116" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="S115" s="4" t="s">
+      <c r="Q116" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="T115" s="4" t="s">
+      <c r="R116" s="4" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+      <c r="S116" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="T116" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
         <v>262</v>
       </c>
@@ -7842,41 +7853,41 @@
         <v>263</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="6" t="s">
+    <row r="118" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="1" t="s">
         <v>264</v>
       </c>
       <c r="B118" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="C118" s="6"/>
-      <c r="D118" s="6"/>
-      <c r="E118" s="6"/>
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="6"/>
-      <c r="K118" s="6"/>
-      <c r="L118" s="6"/>
-      <c r="M118" s="6"/>
-      <c r="N118" s="6"/>
-      <c r="O118" s="6"/>
-      <c r="P118" s="6"/>
-      <c r="Q118" s="6"/>
-      <c r="R118" s="6"/>
-      <c r="S118" s="6"/>
-      <c r="T118" s="6"/>
-    </row>
-    <row r="119" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+    </row>
+    <row r="119" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="B119" s="8" t="s">
+      <c r="B119" s="4" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="6"/>
+      <c r="F119" s="6"/>
+      <c r="G119" s="6"/>
+      <c r="H119" s="6"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="6"/>
+      <c r="K119" s="6"/>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="6"/>
+      <c r="O119" s="6"/>
+      <c r="P119" s="6"/>
+      <c r="Q119" s="6"/>
+      <c r="R119" s="6"/>
+      <c r="S119" s="6"/>
+      <c r="T119" s="6"/>
+    </row>
+    <row r="120" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>268</v>
       </c>
@@ -7884,85 +7895,85 @@
         <v>269</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B121" s="4" t="s">
+      <c r="B121" s="8" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="F122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="G122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="H122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="I122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="J122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="K122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="L122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="M122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="N122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="O122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="P122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="Q122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="R122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="S122" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="T122" s="1" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="1" t="s">
         <v>275</v>
       </c>
-    </row>
-    <row r="124" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="P123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="R123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="S123" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="T123" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>276</v>
       </c>
@@ -7970,11 +7981,11 @@
         <v>277</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="4" t="s">
         <v>279</v>
       </c>
     </row>
@@ -7986,15 +7997,15 @@
         <v>281</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="1" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>284</v>
       </c>
@@ -8002,7 +8013,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
         <v>286</v>
       </c>
@@ -8018,7 +8029,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
         <v>290</v>
       </c>
@@ -8026,31 +8037,31 @@
         <v>291</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
         <v>292</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B134" s="8" t="s">
+      <c r="B134" s="4" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="s">
         <v>297</v>
       </c>
@@ -8058,16 +8069,24 @@
         <v>298</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B136" s="4" t="s">
+      <c r="B136" s="8" t="s">
         <v>300</v>
       </c>
     </row>
+    <row r="137" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="B137" s="4" t="s">
+        <v>302</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T135"/>
+  <autoFilter ref="A2:T136"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
